--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="475">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1388,6 +1388,15 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-observation-type"/&gt;
+    &lt;code value="OBSAMENAGEMENT"/&gt;
+    &lt;display value="Observation sur l’aménagement du moyen de transport"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -7584,7 +7593,7 @@
         <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>83</v>
@@ -7642,7 +7651,7 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>212</v>
@@ -7659,10 +7668,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7780,10 +7789,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7853,16 +7862,16 @@
         <v>83</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>368</v>
@@ -7903,10 +7912,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7929,19 +7938,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7990,7 +7999,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8014,10 +8023,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8028,10 +8037,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8057,16 +8066,16 @@
         <v>361</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8115,7 +8124,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8139,10 +8148,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8153,10 +8162,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8182,13 +8191,13 @@
         <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
         <v>273</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>275</v>
@@ -8240,7 +8249,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8255,13 +8264,13 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>280</v>
@@ -8278,10 +8287,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8307,13 +8316,13 @@
         <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>287</v>
@@ -8365,7 +8374,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8403,10 +8412,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8490,7 +8499,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8528,10 +8537,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8557,10 +8566,10 @@
         <v>84</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>355</v>
@@ -8615,7 +8624,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2434" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>TDDUI Obervation Mobilite Usager</t>
+    <t>TDDUI Observation Mobilite Usager</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -723,6 +723,127 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>Observation.subject.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.subject.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.subject.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Usager</t>
+  </si>
+  <si>
+    <t>Observation.subject.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.subject.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.subject.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>Observation.focus</t>
   </si>
   <si>
@@ -918,9 +1039,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1145,29 +1263,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1407,16 +1503,6 @@
   </si>
   <si>
     <t>Observation.component.code.extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Observation.component.code.coding</t>
@@ -1810,7 +1896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ55"/>
+  <dimension ref="A1:AQ61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
@@ -3978,7 +4064,7 @@
         <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>83</v>
@@ -3987,7 +4073,7 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>227</v>
@@ -3998,9 +4084,7 @@
       <c r="M18" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -4049,19 +4133,19 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -4073,13 +4157,13 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>231</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>83</v>
@@ -4094,14 +4178,14 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4110,23 +4194,21 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4162,49 +4244,49 @@
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>83</v>
+        <v>236</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>83</v>
@@ -4212,14 +4294,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4238,20 +4320,18 @@
         <v>96</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4299,7 +4379,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4308,28 +4388,28 @@
         <v>95</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>83</v>
@@ -4337,10 +4417,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4363,16 +4443,16 @@
         <v>96</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>255</v>
+        <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4398,13 +4478,13 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -4422,7 +4502,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4446,13 +4526,13 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>260</v>
+        <v>138</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>83</v>
@@ -4460,10 +4540,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4474,7 +4554,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4486,18 +4566,18 @@
         <v>96</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4545,13 +4625,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4563,19 +4643,19 @@
         <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>267</v>
+        <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>270</v>
+        <v>83</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>83</v>
@@ -4583,10 +4663,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4609,20 +4689,18 @@
         <v>96</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4646,11 +4724,13 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -4668,7 +4748,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4677,39 +4757,39 @@
         <v>95</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4720,7 +4800,7 @@
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>83</v>
@@ -4729,23 +4809,21 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>193</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
@@ -4769,13 +4847,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4793,16 +4871,16 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>107</v>
@@ -4817,13 +4895,13 @@
         <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>292</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>83</v>
@@ -4831,21 +4909,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4854,22 +4932,22 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4894,13 +4972,13 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -4918,13 +4996,13 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
@@ -4936,41 +5014,41 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>83</v>
+        <v>280</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -4979,22 +5057,22 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>309</v>
+        <v>286</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5043,13 +5121,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -5061,19 +5139,19 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>83</v>
@@ -5081,10 +5159,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5104,19 +5182,19 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>193</v>
+        <v>293</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5142,13 +5220,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5166,7 +5244,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5187,27 +5265,27 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5218,7 +5296,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5227,22 +5305,20 @@
         <v>83</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>193</v>
+        <v>301</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5267,13 +5343,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5291,13 +5367,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5309,19 +5385,19 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>83</v>
@@ -5329,10 +5405,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5352,21 +5428,23 @@
         <v>83</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>334</v>
+        <v>193</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5390,13 +5468,11 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5414,7 +5490,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5423,39 +5499,39 @@
         <v>95</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>341</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5478,18 +5554,20 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>343</v>
+        <v>193</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
       </c>
@@ -5513,13 +5591,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5537,7 +5615,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5546,7 +5624,7 @@
         <v>95</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>107</v>
@@ -5558,31 +5636,31 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>348</v>
+        <v>138</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5601,19 +5679,19 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>352</v>
+        <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5638,13 +5716,13 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
+        <v>249</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5662,7 +5740,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5674,7 +5752,7 @@
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>357</v>
+        <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5683,27 +5761,27 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5714,7 +5792,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5726,16 +5804,20 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5783,19 +5865,19 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5807,10 +5889,10 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>83</v>
+        <v>348</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5821,21 +5903,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5847,16 +5929,16 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>142</v>
+        <v>351</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>144</v>
+        <v>353</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5882,13 +5964,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5906,19 +5988,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5927,62 +6009,62 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>144</v>
+        <v>364</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6007,13 +6089,13 @@
         <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>83</v>
+        <v>367</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -6031,19 +6113,19 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6055,10 +6137,10 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>83</v>
+        <v>368</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>138</v>
+        <v>369</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6069,10 +6151,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6095,15 +6177,17 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6152,7 +6236,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6161,7 +6245,7 @@
         <v>95</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>107</v>
@@ -6173,27 +6257,27 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>83</v>
+        <v>378</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6216,15 +6300,17 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6273,7 +6359,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6282,7 +6368,7 @@
         <v>95</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>107</v>
@@ -6294,27 +6380,27 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>384</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6325,7 +6411,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6337,19 +6423,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>193</v>
+        <v>389</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6374,13 +6460,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6398,19 +6484,19 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>107</v>
+        <v>394</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
@@ -6419,13 +6505,13 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>303</v>
+        <v>396</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6436,10 +6522,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6450,7 +6536,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6462,20 +6548,16 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>395</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6499,13 +6581,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6523,19 +6605,19 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>394</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
@@ -6544,13 +6626,13 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -6561,21 +6643,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6587,18 +6669,18 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>402</v>
+        <v>141</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>142</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>405</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6646,19 +6728,19 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>401</v>
+        <v>237</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>83</v>
@@ -6673,7 +6755,7 @@
         <v>83</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>406</v>
+        <v>231</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6684,42 +6766,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>141</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6767,19 +6853,19 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>83</v>
@@ -6791,10 +6877,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>379</v>
+        <v>83</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>410</v>
+        <v>138</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6805,10 +6891,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6819,7 +6905,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6828,20 +6914,18 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6890,16 +6974,16 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>107</v>
@@ -6914,10 +6998,10 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -6928,10 +7012,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6942,7 +7026,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6951,20 +7035,18 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>422</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7013,16 +7095,16 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>107</v>
@@ -7037,10 +7119,10 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7051,10 +7133,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7065,7 +7147,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7074,22 +7156,22 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7114,13 +7196,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7138,13 +7220,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7159,13 +7241,13 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>430</v>
+        <v>340</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7176,10 +7258,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7190,7 +7272,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7202,16 +7284,20 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>361</v>
+        <v>193</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7235,13 +7321,13 @@
         <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>83</v>
@@ -7259,19 +7345,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7280,13 +7366,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7297,21 +7383,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7323,18 +7409,18 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>141</v>
+        <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>142</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7382,19 +7468,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7409,7 +7495,7 @@
         <v>83</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>365</v>
+        <v>436</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7420,46 +7506,42 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>371</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7507,19 +7589,19 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7531,10 +7613,10 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>138</v>
+        <v>440</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7545,10 +7627,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7556,10 +7638,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7571,20 +7653,18 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>193</v>
+        <v>442</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7593,7 +7673,7 @@
         <v>83</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>83</v>
@@ -7608,11 +7688,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7630,13 +7712,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7651,16 +7733,16 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>213</v>
+        <v>447</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>83</v>
@@ -7668,10 +7750,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7682,7 +7764,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7691,18 +7773,20 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>362</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>451</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7751,19 +7835,19 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>364</v>
+        <v>448</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>83</v>
@@ -7775,10 +7859,10 @@
         <v>83</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>365</v>
+        <v>453</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -7789,14 +7873,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7812,21 +7896,23 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>141</v>
+        <v>389</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>142</v>
+        <v>455</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7862,19 +7948,19 @@
         <v>83</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>454</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7886,7 +7972,7 @@
         <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
@@ -7898,10 +7984,10 @@
         <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>365</v>
+        <v>460</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>83</v>
@@ -7912,10 +7998,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7923,7 +8009,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>95</v>
@@ -7935,23 +8021,19 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>446</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>228</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7999,19 +8081,19 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>230</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
@@ -8023,10 +8105,10 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>453</v>
+        <v>231</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8037,21 +8119,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8060,23 +8142,21 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>361</v>
+        <v>141</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>142</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>233</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8124,19 +8204,19 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>459</v>
+        <v>237</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -8148,10 +8228,10 @@
         <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>461</v>
+        <v>231</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8162,45 +8242,45 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>361</v>
+        <v>141</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>401</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>273</v>
+        <v>402</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
+        <v>144</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8249,48 +8329,48 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8298,7 +8378,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>95</v>
@@ -8310,22 +8390,22 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>193</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>287</v>
+        <v>207</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8335,7 +8415,7 @@
         <v>83</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>83</v>
@@ -8350,13 +8430,11 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>290</v>
+        <v>209</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8374,16 +8452,16 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -8395,16 +8473,16 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>83</v>
@@ -8412,21 +8490,21 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8438,20 +8516,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8475,13 +8549,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8499,19 +8573,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>230</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8520,31 +8594,31 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>302</v>
+        <v>83</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8563,20 +8637,18 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>473</v>
+        <v>142</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>474</v>
+        <v>233</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8612,19 +8684,19 @@
         <v>83</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>83</v>
+        <v>234</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>83</v>
+        <v>235</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>83</v>
+        <v>236</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>472</v>
+        <v>237</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8636,27 +8708,777 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
+      <c r="AK56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ57" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ58" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite-usager.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
